--- a/output/loan_assessment.xlsx
+++ b/output/loan_assessment.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Credit Assessment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Assessment" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="129" customWidth="1" min="3" max="3"/>
+    <col width="140" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Mrs. SEEMA  LODHA</t>
+          <t>LTD</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>10000950117</t>
+          <t>57500001116530</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>IDFC First Bank</t>
+          <t>HDFC Bank</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>364</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>3828019.23</v>
+        <v>297355687.11</v>
       </c>
     </row>
     <row r="9">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>558.74</v>
+        <v>2617041.59</v>
       </c>
     </row>
     <row r="10">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1852937.23</v>
+        <v>297355687.11</v>
       </c>
     </row>
     <row r="11">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>26399132.65</v>
+        <v>1762279898.61</v>
       </c>
     </row>
     <row r="12">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>27065995</v>
+        <v>1500985207.95</v>
       </c>
     </row>
     <row r="13">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>187</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>180</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15">
@@ -705,7 +705,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Moderate balance maintenance with occasional cash flow contractions. Suitable for collateralized loans or lower credit limits.</t>
+          <t>The account shows positive cash flows, stable average monthly balances, and low default risk. Recommended for standard credit facilities.</t>
         </is>
       </c>
     </row>
